--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484103_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484103_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.2356</v>
+        <v>8.0915</v>
       </c>
       <c r="E2" t="n">
-        <v>6.9363</v>
+        <v>5.8763</v>
       </c>
       <c r="F2" t="n">
-        <v>2.2993</v>
+        <v>2.2151</v>
       </c>
       <c r="G2" t="n">
         <v>4.8874</v>
@@ -610,13 +610,13 @@
         <v>1.7855</v>
       </c>
       <c r="S2" t="n">
-        <v>2.2112</v>
+        <v>1.067</v>
       </c>
       <c r="T2" t="n">
-        <v>1.8762</v>
+        <v>0.8163</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3349</v>
+        <v>0.2507</v>
       </c>
       <c r="V2" t="n">
         <v>0.55</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>8.4361</v>
+        <v>7.8965</v>
       </c>
       <c r="E3" t="n">
-        <v>7.7909</v>
+        <v>7.139</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6453</v>
+        <v>0.7575</v>
       </c>
       <c r="G3" t="n">
         <v>8.335100000000001</v>
@@ -688,13 +688,13 @@
         <v>2.7774</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2336</v>
+        <v>-0.3061</v>
       </c>
       <c r="T3" t="n">
-        <v>0.9353</v>
+        <v>0.2835</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.7018</v>
+        <v>-0.5896</v>
       </c>
       <c r="V3" t="n">
         <v>-0.7277</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>D. LORAS MONTERO</t>
+          <t>A. DUCH BELTRAN</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.8261</v>
+        <v>5.3369</v>
       </c>
       <c r="E4" t="n">
-        <v>1.5749</v>
+        <v>4.4074</v>
       </c>
       <c r="F4" t="n">
-        <v>3.2511</v>
+        <v>0.9295</v>
       </c>
       <c r="G4" t="n">
-        <v>4.3354</v>
+        <v>5.1177</v>
       </c>
       <c r="H4" t="n">
-        <v>3.0593</v>
+        <v>1.5266</v>
       </c>
       <c r="I4" t="n">
-        <v>1.2761</v>
+        <v>3.5911</v>
       </c>
       <c r="J4" t="n">
-        <v>4.2389</v>
+        <v>4.0738</v>
       </c>
       <c r="K4" t="n">
-        <v>3.5134</v>
+        <v>1.1694</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7255</v>
+        <v>2.9044</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0965</v>
+        <v>1.0439</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.4542</v>
+        <v>0.3572</v>
       </c>
       <c r="O4" t="n">
-        <v>0.5507</v>
+        <v>0.6867</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1.1903</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.9838</v>
+        <v>-0.9919</v>
       </c>
       <c r="R4" t="n">
-        <v>1.9838</v>
+        <v>2.1822</v>
       </c>
       <c r="S4" t="n">
-        <v>1.0939</v>
+        <v>-0.3146</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.0056</v>
+        <v>0.1191</v>
       </c>
       <c r="U4" t="n">
-        <v>1.0995</v>
+        <v>-0.4337</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.6032</v>
+        <v>-0.6564</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.6745</v>
+        <v>1.2065</v>
       </c>
       <c r="X4" t="n">
-        <v>0.0713</v>
+        <v>-1.8629</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. DUCH BELTRAN</t>
+          <t>D. FERNANDEZ STEFANUTO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4.6358</v>
+        <v>4.9535</v>
       </c>
       <c r="E5" t="n">
-        <v>3.8746</v>
+        <v>3.74</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7612</v>
+        <v>1.2135</v>
       </c>
       <c r="G5" t="n">
-        <v>5.1177</v>
+        <v>3.3516</v>
       </c>
       <c r="H5" t="n">
-        <v>1.5266</v>
+        <v>1.3254</v>
       </c>
       <c r="I5" t="n">
-        <v>3.5911</v>
+        <v>2.0262</v>
       </c>
       <c r="J5" t="n">
-        <v>4.0738</v>
+        <v>1.906</v>
       </c>
       <c r="K5" t="n">
-        <v>1.1694</v>
+        <v>0.6961000000000001</v>
       </c>
       <c r="L5" t="n">
-        <v>2.9044</v>
+        <v>1.21</v>
       </c>
       <c r="M5" t="n">
-        <v>1.0439</v>
+        <v>1.4455</v>
       </c>
       <c r="N5" t="n">
-        <v>0.3572</v>
+        <v>0.6293</v>
       </c>
       <c r="O5" t="n">
-        <v>0.6867</v>
+        <v>0.8162</v>
       </c>
       <c r="P5" t="n">
-        <v>1.1903</v>
+        <v>-0.5952</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9919</v>
+        <v>-1.9838</v>
       </c>
       <c r="R5" t="n">
-        <v>2.1822</v>
+        <v>1.3887</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.0157</v>
+        <v>0.1034</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.4137</v>
+        <v>0.1984</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.602</v>
+        <v>-0.095</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.6564</v>
+        <v>2.0938</v>
       </c>
       <c r="W5" t="n">
-        <v>1.2065</v>
+        <v>3.6194</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.8629</v>
+        <v>-1.5256</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. FERNANDEZ STEFANUTO</t>
+          <t>D. LORAS MONTERO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>4.4652</v>
+        <v>4.6702</v>
       </c>
       <c r="E6" t="n">
-        <v>3.1675</v>
+        <v>1.6996</v>
       </c>
       <c r="F6" t="n">
-        <v>1.2977</v>
+        <v>2.9706</v>
       </c>
       <c r="G6" t="n">
-        <v>3.3516</v>
+        <v>4.3354</v>
       </c>
       <c r="H6" t="n">
-        <v>1.3254</v>
+        <v>3.0593</v>
       </c>
       <c r="I6" t="n">
-        <v>2.0262</v>
+        <v>1.2761</v>
       </c>
       <c r="J6" t="n">
-        <v>1.906</v>
+        <v>4.2389</v>
       </c>
       <c r="K6" t="n">
-        <v>0.6961000000000001</v>
+        <v>3.5134</v>
       </c>
       <c r="L6" t="n">
-        <v>1.21</v>
+        <v>0.7255</v>
       </c>
       <c r="M6" t="n">
-        <v>1.4455</v>
+        <v>0.0965</v>
       </c>
       <c r="N6" t="n">
-        <v>0.6293</v>
+        <v>-0.4542</v>
       </c>
       <c r="O6" t="n">
-        <v>0.8162</v>
+        <v>0.5507</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.5952</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>-1.9838</v>
       </c>
       <c r="R6" t="n">
-        <v>1.3887</v>
+        <v>1.9838</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.3849</v>
+        <v>0.9381</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3741</v>
+        <v>0.1191</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0109</v>
+        <v>0.819</v>
       </c>
       <c r="V6" t="n">
-        <v>2.0938</v>
+        <v>-0.6032</v>
       </c>
       <c r="W6" t="n">
-        <v>3.6194</v>
+        <v>-0.6745</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.5256</v>
+        <v>0.0713</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. BUSCAIL BRIANSO</t>
+          <t>A. SENGHOR</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>3.4586</v>
+        <v>3.0578</v>
       </c>
       <c r="E7" t="n">
-        <v>2.1271</v>
+        <v>1.0362</v>
       </c>
       <c r="F7" t="n">
-        <v>1.3315</v>
+        <v>2.0216</v>
       </c>
       <c r="G7" t="n">
-        <v>3.9403</v>
+        <v>3.6752</v>
       </c>
       <c r="H7" t="n">
-        <v>1.971</v>
+        <v>0.2018</v>
       </c>
       <c r="I7" t="n">
-        <v>1.9693</v>
+        <v>3.4734</v>
       </c>
       <c r="J7" t="n">
-        <v>3.485</v>
+        <v>2.969</v>
       </c>
       <c r="K7" t="n">
-        <v>2.4809</v>
+        <v>0.3183</v>
       </c>
       <c r="L7" t="n">
-        <v>1.004</v>
+        <v>2.6507</v>
       </c>
       <c r="M7" t="n">
-        <v>0.4553</v>
+        <v>0.7062</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.51</v>
+        <v>-0.1165</v>
       </c>
       <c r="O7" t="n">
-        <v>0.9653</v>
+        <v>0.8227</v>
       </c>
       <c r="P7" t="n">
-        <v>0.9919</v>
+        <v>-0.1984</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.9838</v>
+        <v>-2.1822</v>
       </c>
       <c r="R7" t="n">
-        <v>2.9758</v>
+        <v>1.9838</v>
       </c>
       <c r="S7" t="n">
-        <v>1.0639</v>
+        <v>-0.1531</v>
       </c>
       <c r="T7" t="n">
-        <v>0.6973</v>
+        <v>0.2495</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3666</v>
+        <v>-0.4025</v>
       </c>
       <c r="V7" t="n">
-        <v>-2.5374</v>
+        <v>-0.266</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.0713</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-2.4661</v>
+        <v>-0.266</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. SENGHOR</t>
+          <t>J. CAMPENY LLOVERAS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>3.1995</v>
+        <v>2.9872</v>
       </c>
       <c r="E8" t="n">
-        <v>1.1779</v>
+        <v>2.2824</v>
       </c>
       <c r="F8" t="n">
-        <v>2.0216</v>
+        <v>0.7048</v>
       </c>
       <c r="G8" t="n">
-        <v>3.6752</v>
+        <v>2.7024</v>
       </c>
       <c r="H8" t="n">
-        <v>0.2018</v>
+        <v>1.7787</v>
       </c>
       <c r="I8" t="n">
-        <v>3.4734</v>
+        <v>0.9237</v>
       </c>
       <c r="J8" t="n">
-        <v>2.969</v>
+        <v>1.7339</v>
       </c>
       <c r="K8" t="n">
-        <v>0.3183</v>
+        <v>1.0887</v>
       </c>
       <c r="L8" t="n">
-        <v>2.6507</v>
+        <v>0.6451</v>
       </c>
       <c r="M8" t="n">
-        <v>0.7062</v>
+        <v>0.9685</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.1165</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="O8" t="n">
-        <v>0.8227</v>
+        <v>0.2786</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.1984</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.1822</v>
+        <v>-0.9919</v>
       </c>
       <c r="R8" t="n">
-        <v>1.9838</v>
+        <v>0.9919</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0113</v>
+        <v>0.6221</v>
       </c>
       <c r="T8" t="n">
-        <v>0.3912</v>
+        <v>0.06809999999999999</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4025</v>
+        <v>0.554</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.266</v>
+        <v>-0.3373</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.4724</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.266</v>
+        <v>-1.8097</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. CAMPENY LLOVERAS</t>
+          <t>M. BUSCAIL BRIANSO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>2.4723</v>
+        <v>2.8666</v>
       </c>
       <c r="E9" t="n">
-        <v>1.8517</v>
+        <v>1.8437</v>
       </c>
       <c r="F9" t="n">
-        <v>0.6206</v>
+        <v>1.0229</v>
       </c>
       <c r="G9" t="n">
-        <v>2.7024</v>
+        <v>3.9403</v>
       </c>
       <c r="H9" t="n">
-        <v>1.7787</v>
+        <v>1.971</v>
       </c>
       <c r="I9" t="n">
-        <v>0.9237</v>
+        <v>1.9693</v>
       </c>
       <c r="J9" t="n">
-        <v>1.7339</v>
+        <v>3.485</v>
       </c>
       <c r="K9" t="n">
-        <v>1.0887</v>
+        <v>2.4809</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6451</v>
+        <v>1.004</v>
       </c>
       <c r="M9" t="n">
-        <v>0.9685</v>
+        <v>0.4553</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6899999999999999</v>
+        <v>-0.51</v>
       </c>
       <c r="O9" t="n">
-        <v>0.2786</v>
+        <v>0.9653</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>0.9919</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9919</v>
+        <v>-1.9838</v>
       </c>
       <c r="R9" t="n">
-        <v>0.9919</v>
+        <v>2.9758</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1071</v>
+        <v>0.4718</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3627</v>
+        <v>0.4139</v>
       </c>
       <c r="U9" t="n">
-        <v>0.4698</v>
+        <v>0.058</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.3373</v>
+        <v>-2.5374</v>
       </c>
       <c r="W9" t="n">
-        <v>1.4724</v>
+        <v>-0.0713</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.8097</v>
+        <v>-2.4661</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. LOPEZ SAURA</t>
+          <t>T. KOHAN LÓPEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>1.0554</v>
+        <v>1.2652</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.2084</v>
+        <v>-0.1489</v>
       </c>
       <c r="F10" t="n">
-        <v>2.2637</v>
+        <v>1.4141</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.4455</v>
+        <v>1.6488</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.6152</v>
+        <v>-0.2674</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1697</v>
+        <v>1.9162</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.3355</v>
+        <v>1.8292</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1815</v>
+        <v>0.4637</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.517</v>
+        <v>1.3655</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.11</v>
+        <v>-0.1805</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.7967</v>
+        <v>-0.7311</v>
       </c>
       <c r="O10" t="n">
-        <v>0.6867</v>
+        <v>0.5507</v>
       </c>
       <c r="P10" t="n">
+        <v>-0.3968</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>-1.9838</v>
+      </c>
+      <c r="R10" t="n">
         <v>1.5871</v>
       </c>
-      <c r="Q10" t="n">
-        <v>-0.1984</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.7855</v>
-      </c>
       <c r="S10" t="n">
-        <v>-0.0862</v>
+        <v>0.2792</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6744</v>
+        <v>0.0057</v>
       </c>
       <c r="U10" t="n">
-        <v>0.5883</v>
+        <v>0.2734</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-0.266</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-0.266</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>T. KOHAN LÓPEZ</t>
+          <t>M. LOPEZ SAURA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.7564</v>
+        <v>1.1699</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.5174</v>
+        <v>-0.9817</v>
       </c>
       <c r="F11" t="n">
-        <v>1.2738</v>
+        <v>2.1515</v>
       </c>
       <c r="G11" t="n">
-        <v>1.6488</v>
+        <v>-0.4455</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.2674</v>
+        <v>-0.6152</v>
       </c>
       <c r="I11" t="n">
-        <v>1.9162</v>
+        <v>0.1697</v>
       </c>
       <c r="J11" t="n">
-        <v>1.8292</v>
+        <v>-0.3355</v>
       </c>
       <c r="K11" t="n">
-        <v>0.4637</v>
+        <v>0.1815</v>
       </c>
       <c r="L11" t="n">
-        <v>1.3655</v>
+        <v>-0.517</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.1805</v>
+        <v>-0.11</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.7311</v>
+        <v>-0.7967</v>
       </c>
       <c r="O11" t="n">
-        <v>0.5507</v>
+        <v>0.6867</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.3968</v>
+        <v>1.5871</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.9838</v>
+        <v>-0.1984</v>
       </c>
       <c r="R11" t="n">
-        <v>1.5871</v>
+        <v>1.7855</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.2296</v>
+        <v>0.0283</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3627</v>
+        <v>-0.4477</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1332</v>
+        <v>0.4761</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.266</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.266</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0008</v>
+        <v>0.9675</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.5417999999999999</v>
+        <v>0.1724</v>
       </c>
       <c r="F12" t="n">
-        <v>0.5426</v>
+        <v>0.7951</v>
       </c>
       <c r="G12" t="n">
         <v>2.9471</v>
@@ -1390,13 +1390,13 @@
         <v>1.9838</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.4268</v>
+        <v>0.5399</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.2267</v>
+        <v>0.4875</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2001</v>
+        <v>0.0524</v>
       </c>
       <c r="V12" t="n">
         <v>-0.3373</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.1718</v>
+        <v>-0.9575</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.0434</v>
+        <v>-0.9414</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.1284</v>
+        <v>-0.0162</v>
       </c>
       <c r="G13" t="n">
         <v>-1.5073</v>
@@ -1468,13 +1468,13 @@
         <v>0.3968</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.0612</v>
+        <v>0.153</v>
       </c>
       <c r="T13" t="n">
-        <v>0.136</v>
+        <v>0.2381</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1973</v>
+        <v>-0.08500000000000001</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,10 +1501,10 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>41.37</v>
+        <v>42.3053</v>
       </c>
       <c r="E14" t="n">
-        <v>25.1899</v>
+        <v>26.125</v>
       </c>
       <c r="F14" t="n">
         <v>16.18</v>
@@ -1546,19 +1546,19 @@
         <v>21.82229999999999</v>
       </c>
       <c r="S14" t="n">
-        <v>2.494</v>
+        <v>3.429000000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>1.6161</v>
+        <v>2.5515</v>
       </c>
       <c r="U14" t="n">
-        <v>0.8776999999999999</v>
+        <v>0.8778000000000001</v>
       </c>
       <c r="V14" t="n">
-        <v>-3.087499999999999</v>
+        <v>-3.0875</v>
       </c>
       <c r="W14" t="n">
-        <v>7.8229</v>
+        <v>7.822900000000001</v>
       </c>
       <c r="X14" t="n">
         <v>-10.9104</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-1.0986</v>
+        <v>-0.7603</v>
       </c>
       <c r="E15" t="n">
-        <v>0.4198</v>
+        <v>0.3178</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.5184</v>
+        <v>-1.078</v>
       </c>
       <c r="G15" t="n">
         <v>-1.125</v>
@@ -1624,13 +1624,13 @@
         <v>1.7855</v>
       </c>
       <c r="S15" t="n">
-        <v>0.0102</v>
+        <v>0.3486</v>
       </c>
       <c r="T15" t="n">
-        <v>0.5159</v>
+        <v>0.4138</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.5056</v>
+        <v>-0.06519999999999999</v>
       </c>
       <c r="V15" t="n">
         <v>1.2065</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. MALO MONTORIO</t>
+          <t>T. SARTOR</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.6908</v>
+        <v>-1.5141</v>
       </c>
       <c r="E16" t="n">
-        <v>0.3504</v>
+        <v>0.1622</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.0412</v>
+        <v>-1.6763</v>
       </c>
       <c r="G16" t="n">
-        <v>-3.0486</v>
+        <v>-2.8298</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.3733</v>
+        <v>1.6838</v>
       </c>
       <c r="I16" t="n">
-        <v>-2.6753</v>
+        <v>-4.5137</v>
       </c>
       <c r="J16" t="n">
-        <v>1.3561</v>
+        <v>1.7602</v>
       </c>
       <c r="K16" t="n">
-        <v>2.0363</v>
+        <v>3.0805</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.6802</v>
+        <v>-1.3202</v>
       </c>
       <c r="M16" t="n">
-        <v>-4.4047</v>
+        <v>-4.5901</v>
       </c>
       <c r="N16" t="n">
-        <v>-2.4096</v>
+        <v>-1.3967</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.9951</v>
+        <v>-3.1934</v>
       </c>
       <c r="P16" t="n">
-        <v>-2.1822</v>
+        <v>-0.7935</v>
       </c>
       <c r="Q16" t="n">
         <v>-3.9677</v>
       </c>
       <c r="R16" t="n">
-        <v>1.7855</v>
+        <v>3.1741</v>
       </c>
       <c r="S16" t="n">
-        <v>0.5952</v>
+        <v>-0.2324</v>
       </c>
       <c r="T16" t="n">
-        <v>0.0171</v>
+        <v>-0.238</v>
       </c>
       <c r="U16" t="n">
-        <v>0.5780999999999999</v>
+        <v>0.0056</v>
       </c>
       <c r="V16" t="n">
-        <v>2.9449</v>
+        <v>2.3417</v>
       </c>
       <c r="W16" t="n">
-        <v>2.9449</v>
+        <v>2.6076</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-0.266</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>T. SARTOR</t>
+          <t>J. MALO MONTORIO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-2.5344</v>
+        <v>-1.9713</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.45</v>
+        <v>0.3504</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.0844</v>
+        <v>-2.3217</v>
       </c>
       <c r="G17" t="n">
-        <v>-2.8298</v>
+        <v>-3.0486</v>
       </c>
       <c r="H17" t="n">
-        <v>1.6838</v>
+        <v>-0.3733</v>
       </c>
       <c r="I17" t="n">
-        <v>-4.5137</v>
+        <v>-2.6753</v>
       </c>
       <c r="J17" t="n">
-        <v>1.7602</v>
+        <v>1.3561</v>
       </c>
       <c r="K17" t="n">
-        <v>3.0805</v>
+        <v>2.0363</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.3202</v>
+        <v>-0.6802</v>
       </c>
       <c r="M17" t="n">
-        <v>-4.5901</v>
+        <v>-4.4047</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.3967</v>
+        <v>-2.4096</v>
       </c>
       <c r="O17" t="n">
-        <v>-3.1934</v>
+        <v>-1.9951</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.7935</v>
+        <v>-2.1822</v>
       </c>
       <c r="Q17" t="n">
         <v>-3.9677</v>
       </c>
       <c r="R17" t="n">
-        <v>3.1741</v>
+        <v>1.7855</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.2526</v>
+        <v>0.3146</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.8501</v>
+        <v>0.0171</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.4025</v>
+        <v>0.2975</v>
       </c>
       <c r="V17" t="n">
-        <v>2.3417</v>
+        <v>2.9449</v>
       </c>
       <c r="W17" t="n">
-        <v>2.6076</v>
+        <v>2.9449</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.266</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-3.0912</v>
+        <v>-3.2314</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.9751</v>
+        <v>-1.3832</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.116</v>
+        <v>-1.8482</v>
       </c>
       <c r="G18" t="n">
         <v>-6.7544</v>
@@ -1858,13 +1858,13 @@
         <v>1.7855</v>
       </c>
       <c r="S18" t="n">
-        <v>0.7227</v>
+        <v>0.5824</v>
       </c>
       <c r="T18" t="n">
-        <v>0.771</v>
+        <v>0.3629</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0483</v>
+        <v>0.2196</v>
       </c>
       <c r="V18" t="n">
         <v>2.1469</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>C. DIOP</t>
+          <t>X. ROSÀS MARCO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.3841</v>
+        <v>-3.8694</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.1174</v>
+        <v>0.0176</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.2667</v>
+        <v>-3.8871</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.8096</v>
+        <v>-2.1778</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.8612</v>
+        <v>-2.0107</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.9484</v>
+        <v>-0.1671</v>
       </c>
       <c r="J19" t="n">
-        <v>0.2428</v>
+        <v>0.4828</v>
       </c>
       <c r="K19" t="n">
-        <v>0.2027</v>
+        <v>-0.0043</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0402</v>
+        <v>0.487</v>
       </c>
       <c r="M19" t="n">
-        <v>-3.0525</v>
+        <v>-2.6606</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.0639</v>
+        <v>-2.0064</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.9886</v>
+        <v>-0.6542</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.3968</v>
+        <v>0.7935</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.9838</v>
+        <v>-0.9919</v>
       </c>
       <c r="R19" t="n">
-        <v>1.5871</v>
+        <v>1.7855</v>
       </c>
       <c r="S19" t="n">
-        <v>0.6915</v>
+        <v>-0.0723</v>
       </c>
       <c r="T19" t="n">
-        <v>0.6236</v>
+        <v>0.2608</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0679</v>
+        <v>-0.3331</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.8692</v>
+        <v>-2.4129</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>0.266</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.8692</v>
+        <v>-2.6789</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X. ROSÀS MARCO</t>
+          <t>C. DIOP</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-4.5335</v>
+        <v>-3.9282</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.5945</v>
+        <v>-1.9337</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.939</v>
+        <v>-1.9946</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.1778</v>
+        <v>-2.8096</v>
       </c>
       <c r="H20" t="n">
-        <v>-2.0107</v>
+        <v>-0.8612</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1671</v>
+        <v>-1.9484</v>
       </c>
       <c r="J20" t="n">
-        <v>0.4828</v>
+        <v>0.2428</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.0043</v>
+        <v>0.2027</v>
       </c>
       <c r="L20" t="n">
-        <v>0.487</v>
+        <v>0.0402</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.6606</v>
+        <v>-3.0525</v>
       </c>
       <c r="N20" t="n">
-        <v>-2.0064</v>
+        <v>-1.0639</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.6542</v>
+        <v>-1.9886</v>
       </c>
       <c r="P20" t="n">
-        <v>0.7935</v>
+        <v>-0.3968</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9919</v>
+        <v>-1.9838</v>
       </c>
       <c r="R20" t="n">
-        <v>1.7855</v>
+        <v>1.5871</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.7363</v>
+        <v>0.1474</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3514</v>
+        <v>-0.1926</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3849</v>
+        <v>0.34</v>
       </c>
       <c r="V20" t="n">
-        <v>-2.4129</v>
+        <v>-0.8692</v>
       </c>
       <c r="W20" t="n">
-        <v>0.266</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-2.6789</v>
+        <v>-0.8692</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>R. GER SIERRA</t>
+          <t>K. GUILLET</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-5.0247</v>
+        <v>-4.8052</v>
       </c>
       <c r="E21" t="n">
-        <v>-4.8293</v>
+        <v>-1.7691</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.1953</v>
+        <v>-3.0361</v>
       </c>
       <c r="G21" t="n">
-        <v>-4.1741</v>
+        <v>-4.1529</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.3487</v>
+        <v>-1.3557</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.8254</v>
+        <v>-2.7972</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.8593</v>
+        <v>-1.1627</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.2193</v>
+        <v>0.313</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.64</v>
+        <v>-1.4758</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.3148</v>
+        <v>-2.9901</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.1295</v>
+        <v>-1.6687</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.1853</v>
+        <v>-1.3214</v>
       </c>
       <c r="P21" t="n">
+        <v>1.3887</v>
+      </c>
+      <c r="Q21" t="n">
         <v>0</v>
       </c>
-      <c r="Q21" t="n">
-        <v>-1.9838</v>
-      </c>
       <c r="R21" t="n">
-        <v>1.9838</v>
+        <v>1.3887</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.3186</v>
+        <v>-0.8346</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.9862</v>
+        <v>-0.6064000000000001</v>
       </c>
       <c r="U21" t="n">
-        <v>0.6676</v>
+        <v>-0.2282</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.532</v>
+        <v>-1.2065</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.532</v>
+        <v>-1.2065</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>K. GUILLET</t>
+          <t>R. GER SIERRA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.4437</v>
+        <v>-5.1794</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.0752</v>
+        <v>-4.7273</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.3685</v>
+        <v>-0.4521</v>
       </c>
       <c r="G22" t="n">
-        <v>-4.1529</v>
+        <v>-4.1741</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.3557</v>
+        <v>-2.3487</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.7972</v>
+        <v>-1.8254</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.1627</v>
+        <v>-1.8593</v>
       </c>
       <c r="K22" t="n">
-        <v>0.313</v>
+        <v>-1.2193</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.4758</v>
+        <v>-0.64</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.9901</v>
+        <v>-2.3148</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.6687</v>
+        <v>-1.1295</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.3214</v>
+        <v>-1.1853</v>
       </c>
       <c r="P22" t="n">
-        <v>1.3887</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-1.9838</v>
       </c>
       <c r="R22" t="n">
-        <v>1.3887</v>
+        <v>1.9838</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.4731</v>
+        <v>-0.4733</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.9125</v>
+        <v>-0.8841</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.5606</v>
+        <v>0.4108</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.2065</v>
+        <v>-0.532</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.2065</v>
+        <v>-0.532</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A. FERNANDEZ FUERTES</t>
+          <t>J. MIRANDA VARGAS</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-7.0835</v>
+        <v>-6.9271</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.3545</v>
+        <v>-3.2481</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.729</v>
+        <v>-3.679</v>
       </c>
       <c r="G23" t="n">
-        <v>-9.216799999999999</v>
+        <v>-2.699</v>
       </c>
       <c r="H23" t="n">
-        <v>-3.0641</v>
+        <v>-1.5926</v>
       </c>
       <c r="I23" t="n">
-        <v>-6.1526</v>
+        <v>-1.1064</v>
       </c>
       <c r="J23" t="n">
-        <v>-4.5546</v>
+        <v>-0.1024</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.1938</v>
+        <v>0.6153999999999999</v>
       </c>
       <c r="L23" t="n">
-        <v>-3.3608</v>
+        <v>-0.7178</v>
       </c>
       <c r="M23" t="n">
-        <v>-4.6622</v>
+        <v>-2.5966</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.8703</v>
+        <v>-2.208</v>
       </c>
       <c r="O23" t="n">
-        <v>-2.7918</v>
+        <v>-0.3886</v>
       </c>
       <c r="P23" t="n">
-        <v>0.5952</v>
+        <v>-1.9838</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.9838</v>
+        <v>-2.9758</v>
       </c>
       <c r="R23" t="n">
-        <v>2.579</v>
+        <v>0.9919</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.0056</v>
+        <v>-0.1686</v>
       </c>
       <c r="T23" t="n">
-        <v>0.771</v>
+        <v>-0.17</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.7766</v>
+        <v>0.0014</v>
       </c>
       <c r="V23" t="n">
-        <v>1.5437</v>
+        <v>-2.0757</v>
       </c>
       <c r="W23" t="n">
-        <v>2.4129</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.8692</v>
+        <v>-2.0757</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>J. MIRANDA VARGAS</t>
+          <t>A. FERNANDEZ FUERTES</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-7.4857</v>
+        <v>-7.143</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.5542</v>
+        <v>-3.9667</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.9315</v>
+        <v>-3.1763</v>
       </c>
       <c r="G24" t="n">
-        <v>-2.699</v>
+        <v>-9.216799999999999</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.5926</v>
+        <v>-3.0641</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.1064</v>
+        <v>-6.1526</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.1024</v>
+        <v>-4.5546</v>
       </c>
       <c r="K24" t="n">
-        <v>0.6153999999999999</v>
+        <v>-1.1938</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.7178</v>
+        <v>-3.3608</v>
       </c>
       <c r="M24" t="n">
-        <v>-2.5966</v>
+        <v>-4.6622</v>
       </c>
       <c r="N24" t="n">
-        <v>-2.208</v>
+        <v>-1.8703</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.3886</v>
+        <v>-2.7918</v>
       </c>
       <c r="P24" t="n">
+        <v>0.5952</v>
+      </c>
+      <c r="Q24" t="n">
         <v>-1.9838</v>
       </c>
-      <c r="Q24" t="n">
-        <v>-2.9758</v>
-      </c>
       <c r="R24" t="n">
-        <v>0.9919</v>
+        <v>2.579</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.7272</v>
+        <v>-0.06510000000000001</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.4761</v>
+        <v>0.1588</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.2511</v>
+        <v>-0.224</v>
       </c>
       <c r="V24" t="n">
-        <v>-2.0757</v>
+        <v>1.5437</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>2.4129</v>
       </c>
       <c r="X24" t="n">
-        <v>-2.0757</v>
+        <v>-0.8692</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-41.3702</v>
+        <v>-39.3294</v>
       </c>
       <c r="E25" t="n">
-        <v>-16.18</v>
+        <v>-16.1801</v>
       </c>
       <c r="F25" t="n">
-        <v>-25.19</v>
+        <v>-23.1494</v>
       </c>
       <c r="G25" t="n">
         <v>-38.988</v>
@@ -2377,7 +2377,7 @@
         <v>-26.8178</v>
       </c>
       <c r="J25" t="n">
-        <v>-4.390400000000001</v>
+        <v>-4.3904</v>
       </c>
       <c r="K25" t="n">
         <v>4.516999999999999</v>
@@ -2404,13 +2404,13 @@
         <v>18.8466</v>
       </c>
       <c r="S25" t="n">
-        <v>-2.4938</v>
+        <v>-0.4533</v>
       </c>
       <c r="T25" t="n">
         <v>-0.8776999999999997</v>
       </c>
       <c r="U25" t="n">
-        <v>-1.616</v>
+        <v>0.4244</v>
       </c>
       <c r="V25" t="n">
         <v>3.087400000000001</v>
